--- a/成绩表.xlsx
+++ b/成绩表.xlsx
@@ -2,32 +2,41 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="2745" windowWidth="28800" windowHeight="15345" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="成绩单" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="班级信息" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -39,7 +48,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -63,7 +72,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -427,14 +436,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="4" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
@@ -512,6 +519,18 @@
       <c r="F2" t="n">
         <v>85</v>
       </c>
+      <c r="G2">
+        <f>SUM(D2:F2)</f>
+        <v/>
+      </c>
+      <c r="H2">
+        <f>AVERAGE(D2:F2)</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>IF(H2&gt;=90,"优秀",IF(H2&gt;=75,"良好",IF(H2&gt;=60,"及格","不及格")))</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -538,6 +557,18 @@
       <c r="F3" t="n">
         <v>90</v>
       </c>
+      <c r="G3">
+        <f>SUM(D3:F3)</f>
+        <v/>
+      </c>
+      <c r="H3">
+        <f>AVERAGE(D3:F3)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(H3&gt;=90,"优秀",IF(H3&gt;=75,"良好",IF(H3&gt;=60,"及格","不及格")))</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -556,7 +587,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="E4" t="n">
         <v>88</v>
@@ -564,6 +595,18 @@
       <c r="F4" t="n">
         <v>92</v>
       </c>
+      <c r="G4">
+        <f>SUM(D4:F4)</f>
+        <v/>
+      </c>
+      <c r="H4">
+        <f>AVERAGE(D4:F4)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(H4&gt;=90,"优秀",IF(H4&gt;=75,"良好",IF(H4&gt;=60,"及格","不及格")))</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -590,6 +633,18 @@
       <c r="F5" t="n">
         <v>47</v>
       </c>
+      <c r="G5">
+        <f>SUM(D5:F5)</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>AVERAGE(D5:F5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(H5&gt;=90,"优秀",IF(H5&gt;=75,"良好",IF(H5&gt;=60,"及格","不及格")))</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -616,6 +671,18 @@
       <c r="F6" t="n">
         <v>74</v>
       </c>
+      <c r="G6">
+        <f>SUM(D6:F6)</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>AVERAGE(D6:F6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(H6&gt;=90,"优秀",IF(H6&gt;=75,"良好",IF(H6&gt;=60,"及格","不及格")))</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -642,6 +709,18 @@
       <c r="F7" t="n">
         <v>84</v>
       </c>
+      <c r="G7">
+        <f>SUM(D7:F7)</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>AVERAGE(D7:F7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(H7&gt;=90,"优秀",IF(H7&gt;=75,"良好",IF(H7&gt;=60,"及格","不及格")))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -668,6 +747,18 @@
       <c r="F8" t="n">
         <v>77</v>
       </c>
+      <c r="G8">
+        <f>SUM(D8:F8)</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>AVERAGE(D8:F8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(H8&gt;=90,"优秀",IF(H8&gt;=75,"良好",IF(H8&gt;=60,"及格","不及格")))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -694,6 +785,18 @@
       <c r="F9" t="n">
         <v>81</v>
       </c>
+      <c r="G9">
+        <f>SUM(D9:F9)</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>AVERAGE(D9:F9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(H9&gt;=90,"优秀",IF(H9&gt;=75,"良好",IF(H9&gt;=60,"及格","不及格")))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -720,6 +823,18 @@
       <c r="F10" t="n">
         <v>69</v>
       </c>
+      <c r="G10">
+        <f>SUM(D10:F10)</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>AVERAGE(D10:F10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(H10&gt;=90,"优秀",IF(H10&gt;=75,"良好",IF(H10&gt;=60,"及格","不及格")))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -746,6 +861,18 @@
       <c r="F11" t="n">
         <v>89</v>
       </c>
+      <c r="G11">
+        <f>SUM(D11:F11)</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>AVERAGE(D11:F11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(H11&gt;=90,"优秀",IF(H11&gt;=75,"良好",IF(H11&gt;=60,"及格","不及格")))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -772,6 +899,18 @@
       <c r="F12" t="n">
         <v>72</v>
       </c>
+      <c r="G12">
+        <f>SUM(D12:F12)</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>AVERAGE(D12:F12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(H12&gt;=90,"优秀",IF(H12&gt;=75,"良好",IF(H12&gt;=60,"及格","不及格")))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -798,6 +937,18 @@
       <c r="F13" t="n">
         <v>76</v>
       </c>
+      <c r="G13">
+        <f>SUM(D13:F13)</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>AVERAGE(D13:F13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(H13&gt;=90,"优秀",IF(H13&gt;=75,"良好",IF(H13&gt;=60,"及格","不及格")))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -812,6 +963,10 @@
           <t>数学85分及以上人数</t>
         </is>
       </c>
+      <c r="B16">
+        <f>COUNTIF(E2:E13,"&gt;=85")</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -819,12 +974,20 @@
           <t>高一1班语文平均分</t>
         </is>
       </c>
+      <c r="B17">
+        <f>AVERAGEIF(C2:C13,"高一1班",D2:D13)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
           <t>英语最高分</t>
         </is>
+      </c>
+      <c r="B18">
+        <f>MAX(F2:F13)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -838,12 +1001,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="20.75" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -862,6 +1026,26 @@
           <t>教室</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>班级学生平均总成绩</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>语文平均分</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>数学平均分</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>英语平均分</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -877,6 +1061,22 @@
       <c r="C2" t="n">
         <v>301</v>
       </c>
+      <c r="D2">
+        <f>AVERAGEIF(成绩单!$C$2:$C$13,A2,成绩单!$G$2:$G$13)</f>
+        <v/>
+      </c>
+      <c r="E2">
+        <f>AVERAGEIF(成绩单!$C$2:$C$13,$A2,成绩单!D$2:D$13)</f>
+        <v/>
+      </c>
+      <c r="F2">
+        <f>AVERAGEIF(成绩单!$C$2:$C$13,$A2,成绩单!E$2:E$13)</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>AVERAGEIF(成绩单!$C$2:$C$13,$A2,成绩单!F$2:F$13)</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -892,6 +1092,22 @@
       <c r="C3" t="n">
         <v>302</v>
       </c>
+      <c r="D3">
+        <f>AVERAGEIF(成绩单!$C$2:$C$13,A3,成绩单!$G$2:$G$13)</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>AVERAGEIF(成绩单!$C$2:$C$13,$A3,成绩单!D$2:D$13)</f>
+        <v/>
+      </c>
+      <c r="F3">
+        <f>AVERAGEIF(成绩单!$C$2:$C$13,$A3,成绩单!E$2:E$13)</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>AVERAGEIF(成绩单!$C$2:$C$13,$A3,成绩单!F$2:F$13)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -906,6 +1122,22 @@
       </c>
       <c r="C4" t="n">
         <v>303</v>
+      </c>
+      <c r="D4">
+        <f>AVERAGEIF(成绩单!$C$2:$C$13,A4,成绩单!$G$2:$G$13)</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>AVERAGEIF(成绩单!$C$2:$C$13,$A4,成绩单!D$2:D$13)</f>
+        <v/>
+      </c>
+      <c r="F4">
+        <f>AVERAGEIF(成绩单!$C$2:$C$13,$A4,成绩单!E$2:E$13)</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>AVERAGEIF(成绩单!$C$2:$C$13,$A4,成绩单!F$2:F$13)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
